--- a/StructureDefinition-tk-organization.xlsx
+++ b/StructureDefinition-tk-organization.xlsx
@@ -678,7 +678,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.752.29.4.13</t>
+    <t>urn:oid:2.5.4.97</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>

--- a/StructureDefinition-tk-organization.xlsx
+++ b/StructureDefinition-tk-organization.xlsx
@@ -505,7 +505,7 @@
 </t>
   </si>
   <si>
-    <t>Organisationsidentifierare, inklusive organisationsnummer</t>
+    <t>Organisationsidentifierare ("logisk adress"), inklusive organisationsnummer</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
